--- a/output/pdf_financials_xlsx/NRM.xlsx
+++ b/output/pdf_financials_xlsx/NRM.xlsx
@@ -2488,19 +2488,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.530573</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.558716</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.183938</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>10.386523</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.576523</v>
       </c>
     </row>
     <row r="93">
@@ -3045,19 +3045,19 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.448784</v>
+        <v>0.411338</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.379808</v>
+        <v>0.327958</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.247527</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.78169</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.038163</v>
       </c>
     </row>
     <row r="119">
@@ -4238,7 +4238,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4820,7 +4824,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.530573</v>
       </c>
@@ -5687,7 +5695,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6593,7 +6605,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>-0.037446</v>
       </c>

--- a/output/pdf_financials_xlsx/NRM.xlsx
+++ b/output/pdf_financials_xlsx/NRM.xlsx
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000231</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.033594</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.653772</v>
+        <v>-0.653886</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.605314</v>
+        <v>-0.605545</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.752063</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.152517</v>
+        <v>-3.186111</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.809797</v>
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.653772</v>
+        <v>-0.653886</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.605314</v>
+        <v>-0.605545</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.752063</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.095748</v>
+        <v>-3.129342</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.75698</v>
@@ -1189,10 +1189,10 @@
         <v>0.119989</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.577363</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.114134</v>
       </c>
     </row>
     <row r="35">
@@ -1233,10 +1233,10 @@
         <v>0.119989</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.577363</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.114134</v>
       </c>
     </row>
     <row r="37">
@@ -1497,10 +1497,10 @@
         <v>0.016158</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.722858</v>
+        <v>0.145495</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.284087</v>
+        <v>0.169953</v>
       </c>
     </row>
     <row r="49">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">

--- a/output/pdf_financials_xlsx/NRM.xlsx
+++ b/output/pdf_financials_xlsx/NRM.xlsx
@@ -2671,13 +2671,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.004104</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.01</v>
+        <v>0.004164</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.004163</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0.040049</v>
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.021408</v>
+        <v>0.025512</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.036505</v>
+        <v>0.030669</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.08824</v>
+        <v>0.092403</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.120387</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.003631</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.013015</v>
       </c>
     </row>
     <row r="111">
@@ -5320,7 +5320,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -6363,7 +6367,11 @@
           <t>GST receivables</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.004104</v>
       </c>
@@ -6892,7 +6900,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>-0.031403</v>
       </c>
